--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,6 +1724,4059 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125719365</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>397373</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697676</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125719375</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>397295</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6697668</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125719473</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>397251</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697705</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125718932</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>397401</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697731</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125718708</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>397437</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125716840</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>397730</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697688</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125719337</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>397294</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697669</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125718537</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>397396</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697728</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125718443</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>397480</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6697723</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125719526</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>397373</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6697676</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125719134</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>397331</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6697672</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125718662</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>397408</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6697666</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125718539</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78725</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>397411</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697715</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125717768</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>397538</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6697682</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125719694</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5479</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>397212</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6697719</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125718725</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>397437</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125718601</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>397410</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6697671</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125718584</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>397396</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6697692</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125718195</v>
+      </c>
+      <c r="B29" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>397560</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6697723</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125716739</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>397710</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6697735</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125718716</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>397437</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125718882</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80099</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>397437</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125717751</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>397590</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6697690</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125719501</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>397252</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6697707</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125719032</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91240</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>397343</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6697653</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125718927</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>353</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>397391</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6697659</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125718597</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>397397</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6697674</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125719141</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>397373</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6697657</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125718679</v>
+      </c>
+      <c r="B39" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>397409</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6697661</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125719322</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>397309</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6697695</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125718201</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>397560</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6697723</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125717848</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>397549</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6697680</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125718753</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80105</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>397437</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6697664</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125718900</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>353</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>397402</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6697659</v>
+      </c>
+      <c r="S44" t="n">
+        <v>9</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125718606</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>397397</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6697674</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125718531</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78726</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>397411</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6697715</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125717791</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78999</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>185</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>397585</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6697687</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125719487</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>397214</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6697663</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125718722</v>
+      </c>
+      <c r="B49" t="n">
+        <v>75005</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lövåsen, Lövåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>397402</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6697659</v>
+      </c>
+      <c r="S49" t="n">
+        <v>12</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125718062</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>397526</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6697708</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -4557,32 +4557,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>75005</v>
+        <v>78634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R39" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,39 +4652,39 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125719322</v>
+        <v>125718753</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>80105</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397309</v>
+        <v>397437</v>
       </c>
       <c r="R40" t="n">
-        <v>6697695</v>
+        <v>6697664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,45 +4761,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718201</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>75005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397560</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697723</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125717848</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -4879,17 +4889,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397549</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697680</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,39 +4943,39 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718753</v>
+        <v>125718201</v>
       </c>
       <c r="B43" t="n">
-        <v>80105</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4986,14 +4986,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397437</v>
+        <v>397560</v>
       </c>
       <c r="R43" t="n">
-        <v>6697664</v>
+        <v>6697723</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718900</v>
+        <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,37 +5063,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397402</v>
+        <v>397549</v>
       </c>
       <c r="R44" t="n">
-        <v>6697659</v>
+        <v>6697680</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,12 +5147,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2261,7 +2261,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125716840</v>
+        <v>125719337</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2292,17 +2292,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397730</v>
+        <v>397294</v>
       </c>
       <c r="R16" t="n">
-        <v>6697688</v>
+        <v>6697669</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,9 +2329,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,19 +2356,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125719337</v>
+        <v>125718537</v>
       </c>
       <c r="B17" t="n">
         <v>78967</v>
@@ -2393,10 +2403,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397294</v>
+        <v>397396</v>
       </c>
       <c r="R17" t="n">
-        <v>6697669</v>
+        <v>6697728</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,7 +2438,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2438,7 +2448,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2465,7 +2475,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125718537</v>
+        <v>125716840</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2496,17 +2506,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397396</v>
+        <v>397730</v>
       </c>
       <c r="R18" t="n">
-        <v>6697728</v>
+        <v>6697688</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,19 +2543,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,22 +2560,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718443</v>
+        <v>125719526</v>
       </c>
       <c r="B19" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2583,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397480</v>
+        <v>397373</v>
       </c>
       <c r="R19" t="n">
-        <v>6697723</v>
+        <v>6697676</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,9 +2640,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,22 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719526</v>
+        <v>125719134</v>
       </c>
       <c r="B20" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,13 +2714,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397373</v>
+        <v>397331</v>
       </c>
       <c r="R20" t="n">
-        <v>6697676</v>
+        <v>6697672</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,19 +2747,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719134</v>
+        <v>125718443</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,34 +2787,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397331</v>
+        <v>397480</v>
       </c>
       <c r="R21" t="n">
-        <v>6697672</v>
+        <v>6697723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,45 +2873,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125718662</v>
+        <v>125719694</v>
       </c>
       <c r="B22" t="n">
-        <v>91240</v>
+        <v>5479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>101920</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397408</v>
+        <v>397212</v>
       </c>
       <c r="R22" t="n">
-        <v>6697666</v>
+        <v>6697719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,50 +3179,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125719694</v>
+        <v>125718662</v>
       </c>
       <c r="B25" t="n">
-        <v>5479</v>
+        <v>91247</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101920</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397212</v>
+        <v>397408</v>
       </c>
       <c r="R25" t="n">
-        <v>6697719</v>
+        <v>6697666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125716739</v>
+        <v>125718716</v>
       </c>
       <c r="B30" t="n">
-        <v>91240</v>
+        <v>80071</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3685,34 +3685,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397710</v>
+        <v>397437</v>
       </c>
       <c r="R30" t="n">
-        <v>6697735</v>
+        <v>6697664</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,10 +3771,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718716</v>
+        <v>125716739</v>
       </c>
       <c r="B31" t="n">
-        <v>80071</v>
+        <v>91247</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,34 +3782,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397437</v>
+        <v>397710</v>
       </c>
       <c r="R31" t="n">
-        <v>6697664</v>
+        <v>6697735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718927</v>
+        <v>125718597</v>
       </c>
       <c r="B36" t="n">
-        <v>78634</v>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397391</v>
+        <v>397397</v>
       </c>
       <c r="R36" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R37" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,9 +4421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4438,22 +4448,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125719141</v>
+        <v>125718927</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,13 +4495,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397373</v>
+        <v>397391</v>
       </c>
       <c r="R38" t="n">
-        <v>6697657</v>
+        <v>6697659</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,19 +4528,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,44 +4545,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718900</v>
+        <v>125718679</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>75005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397402</v>
+        <v>397409</v>
       </c>
       <c r="R39" t="n">
-        <v>6697659</v>
+        <v>6697661</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,19 +4625,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4761,32 +4751,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125719322</v>
       </c>
       <c r="B41" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397309</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697695</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125719322</v>
+        <v>125718201</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -4889,14 +4879,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397309</v>
+        <v>397560</v>
       </c>
       <c r="R42" t="n">
-        <v>6697695</v>
+        <v>6697723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4945,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718201</v>
+        <v>125717848</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4990,13 +4980,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397560</v>
+        <v>397549</v>
       </c>
       <c r="R43" t="n">
-        <v>6697723</v>
+        <v>6697680</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,9 +5013,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,60 +5040,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125717848</v>
+        <v>125718606</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>80030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397549</v>
+        <v>397397</v>
       </c>
       <c r="R44" t="n">
-        <v>6697680</v>
+        <v>6697674</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,19 +5120,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,44 +5137,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718606</v>
+        <v>125718900</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>78634</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5194,13 +5184,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397397</v>
+        <v>397402</v>
       </c>
       <c r="R45" t="n">
-        <v>6697674</v>
+        <v>6697659</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,9 +5217,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718601</v>
+        <v>125718716</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397410</v>
+        <v>397437</v>
       </c>
       <c r="R27" t="n">
-        <v>6697671</v>
+        <v>6697664</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,19 +3441,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,22 +3458,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718584</v>
+        <v>125716739</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>91247</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,34 +3481,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397396</v>
+        <v>397710</v>
       </c>
       <c r="R28" t="n">
-        <v>6697692</v>
+        <v>6697735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,45 +3567,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718195</v>
+        <v>125718601</v>
       </c>
       <c r="B29" t="n">
-        <v>75005</v>
+        <v>78967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397560</v>
+        <v>397410</v>
       </c>
       <c r="R29" t="n">
-        <v>6697723</v>
+        <v>6697671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,9 +3635,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,22 +3662,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718716</v>
+        <v>125718584</v>
       </c>
       <c r="B30" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397437</v>
+        <v>397396</v>
       </c>
       <c r="R30" t="n">
-        <v>6697664</v>
+        <v>6697692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,32 +3771,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125716739</v>
+        <v>125718195</v>
       </c>
       <c r="B31" t="n">
-        <v>91247</v>
+        <v>75005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397710</v>
+        <v>397560</v>
       </c>
       <c r="R31" t="n">
-        <v>6697735</v>
+        <v>6697723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125719322</v>
+        <v>125718900</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,21 +4762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397309</v>
+        <v>397402</v>
       </c>
       <c r="R41" t="n">
-        <v>6697695</v>
+        <v>6697659</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,19 +4846,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718201</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -4879,14 +4889,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397560</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697723</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,7 +4955,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125717848</v>
+        <v>125718201</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4980,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397549</v>
+        <v>397560</v>
       </c>
       <c r="R43" t="n">
-        <v>6697680</v>
+        <v>6697723</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5013,19 +5023,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,60 +5040,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718606</v>
+        <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>80030</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397397</v>
+        <v>397549</v>
       </c>
       <c r="R44" t="n">
-        <v>6697674</v>
+        <v>6697680</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,9 +5120,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,44 +5147,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718900</v>
+        <v>125718606</v>
       </c>
       <c r="B45" t="n">
-        <v>78634</v>
+        <v>80030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5184,13 +5194,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397402</v>
+        <v>397397</v>
       </c>
       <c r="R45" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5217,19 +5227,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B47" t="n">
-        <v>78999</v>
+        <v>80070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R47" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,9 +5421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,44 +5448,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>75005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5485,13 +5495,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R48" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5520,7 +5530,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5530,7 +5540,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,60 +5555,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125718722</v>
+        <v>125717791</v>
       </c>
       <c r="B49" t="n">
-        <v>75005</v>
+        <v>78999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397402</v>
+        <v>397585</v>
       </c>
       <c r="R49" t="n">
-        <v>6697659</v>
+        <v>6697687</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5625,19 +5635,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -4557,32 +4557,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>75005</v>
+        <v>78634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R39" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,22 +4652,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718753</v>
+        <v>125718679</v>
       </c>
       <c r="B40" t="n">
-        <v>80105</v>
+        <v>75005</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4665,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397437</v>
+        <v>397409</v>
       </c>
       <c r="R40" t="n">
-        <v>6697664</v>
+        <v>6697661</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,32 +4761,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718900</v>
+        <v>125718753</v>
       </c>
       <c r="B41" t="n">
-        <v>78634</v>
+        <v>80105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4786,13 +4796,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397402</v>
+        <v>397437</v>
       </c>
       <c r="R41" t="n">
-        <v>6697659</v>
+        <v>6697664</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4829,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,12 +4846,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>125719365</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>125719375</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125719473</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125718932</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>125718708</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>125719337</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>125718537</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>125716840</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719526</v>
+        <v>125718443</v>
       </c>
       <c r="B19" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2583,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397373</v>
+        <v>397480</v>
       </c>
       <c r="R19" t="n">
-        <v>6697676</v>
+        <v>6697723</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,19 +2640,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,22 +2657,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719134</v>
+        <v>125719526</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,13 +2704,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397331</v>
+        <v>397373</v>
       </c>
       <c r="R20" t="n">
-        <v>6697672</v>
+        <v>6697676</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,9 +2737,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718443</v>
+        <v>125719134</v>
       </c>
       <c r="B21" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,34 +2787,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397480</v>
+        <v>397331</v>
       </c>
       <c r="R21" t="n">
-        <v>6697723</v>
+        <v>6697672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,50 +2873,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125719694</v>
+        <v>125718662</v>
       </c>
       <c r="B22" t="n">
-        <v>5479</v>
+        <v>91248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101920</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397212</v>
+        <v>397408</v>
       </c>
       <c r="R22" t="n">
-        <v>6697719</v>
+        <v>6697666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2978,7 +2973,7 @@
         <v>125718539</v>
       </c>
       <c r="B23" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3075,7 +3070,7 @@
         <v>125717768</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3179,45 +3174,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125718662</v>
+        <v>125719694</v>
       </c>
       <c r="B25" t="n">
-        <v>91247</v>
+        <v>5479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397408</v>
+        <v>397212</v>
       </c>
       <c r="R25" t="n">
-        <v>6697666</v>
+        <v>6697719</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>125718725</v>
       </c>
       <c r="B26" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718716</v>
+        <v>125718601</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397437</v>
+        <v>397410</v>
       </c>
       <c r="R27" t="n">
-        <v>6697664</v>
+        <v>6697671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,9 +3441,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,12 +3468,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3473,7 +3483,7 @@
         <v>125716739</v>
       </c>
       <c r="B28" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3567,45 +3577,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718601</v>
+        <v>125718195</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>75006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397410</v>
+        <v>397560</v>
       </c>
       <c r="R29" t="n">
-        <v>6697671</v>
+        <v>6697723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,19 +3645,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,12 +3662,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3677,7 +3677,7 @@
         <v>125718584</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3771,45 +3771,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718195</v>
+        <v>125718716</v>
       </c>
       <c r="B31" t="n">
-        <v>75005</v>
+        <v>80072</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397560</v>
+        <v>397437</v>
       </c>
       <c r="R31" t="n">
-        <v>6697723</v>
+        <v>6697664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125718882</v>
+        <v>125717751</v>
       </c>
       <c r="B32" t="n">
-        <v>80099</v>
+        <v>75006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,34 +3879,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397437</v>
+        <v>397590</v>
       </c>
       <c r="R32" t="n">
-        <v>6697664</v>
+        <v>6697690</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125717751</v>
+        <v>125718882</v>
       </c>
       <c r="B33" t="n">
-        <v>75005</v>
+        <v>80100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,34 +3976,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397590</v>
+        <v>397437</v>
       </c>
       <c r="R33" t="n">
-        <v>6697690</v>
+        <v>6697664</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,7 +4065,7 @@
         <v>125719501</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718597</v>
+        <v>125718927</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>78635</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397397</v>
+        <v>397391</v>
       </c>
       <c r="R36" t="n">
-        <v>6697674</v>
+        <v>6697659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
         <v>125719141</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718927</v>
+        <v>125718597</v>
       </c>
       <c r="B38" t="n">
-        <v>78634</v>
+        <v>80071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397391</v>
+        <v>397397</v>
       </c>
       <c r="R38" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4560,7 +4560,7 @@
         <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718679</v>
+        <v>125718753</v>
       </c>
       <c r="B40" t="n">
-        <v>75005</v>
+        <v>80106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397409</v>
+        <v>397437</v>
       </c>
       <c r="R40" t="n">
-        <v>6697661</v>
+        <v>6697664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718753</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>80105</v>
+        <v>75006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397437</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697664</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
         <v>125719322</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>125718201</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>125718606</v>
       </c>
       <c r="B45" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>125718531</v>
       </c>
       <c r="B46" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125719487</v>
+        <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>80070</v>
+        <v>79000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397214</v>
+        <v>397585</v>
       </c>
       <c r="R47" t="n">
-        <v>6697663</v>
+        <v>6697687</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,19 +5421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,44 +5438,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125718722</v>
+        <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>75005</v>
+        <v>80071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5495,13 +5485,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397402</v>
+        <v>397214</v>
       </c>
       <c r="R48" t="n">
-        <v>6697659</v>
+        <v>6697663</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5530,7 +5520,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5540,7 +5530,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5555,60 +5545,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125717791</v>
+        <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>78999</v>
+        <v>75006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397585</v>
+        <v>397402</v>
       </c>
       <c r="R49" t="n">
-        <v>6697687</v>
+        <v>6697659</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5635,9 +5625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125717751</v>
+        <v>125718882</v>
       </c>
       <c r="B32" t="n">
-        <v>75006</v>
+        <v>80100</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,34 +3879,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397590</v>
+        <v>397437</v>
       </c>
       <c r="R32" t="n">
-        <v>6697690</v>
+        <v>6697664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125718882</v>
+        <v>125717751</v>
       </c>
       <c r="B33" t="n">
-        <v>80100</v>
+        <v>75006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,34 +3976,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397437</v>
+        <v>397590</v>
       </c>
       <c r="R33" t="n">
-        <v>6697664</v>
+        <v>6697690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R37" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,19 +4421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4448,22 +4438,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,13 +4485,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R38" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4528,9 +4518,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,44 +4545,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718900</v>
+        <v>125718679</v>
       </c>
       <c r="B39" t="n">
-        <v>78635</v>
+        <v>75006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397402</v>
+        <v>397409</v>
       </c>
       <c r="R39" t="n">
-        <v>6697659</v>
+        <v>6697661</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,19 +4625,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,39 +4642,39 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718753</v>
+        <v>125719322</v>
       </c>
       <c r="B40" t="n">
-        <v>80106</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4699,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397437</v>
+        <v>397309</v>
       </c>
       <c r="R40" t="n">
-        <v>6697664</v>
+        <v>6697695</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,45 +4751,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125718201</v>
       </c>
       <c r="B41" t="n">
-        <v>75006</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397560</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125719322</v>
+        <v>125717848</v>
       </c>
       <c r="B42" t="n">
         <v>78968</v>
@@ -4889,17 +4879,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397309</v>
+        <v>397549</v>
       </c>
       <c r="R42" t="n">
-        <v>6697695</v>
+        <v>6697680</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718201</v>
+        <v>125718900</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,37 +4966,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397560</v>
+        <v>397402</v>
       </c>
       <c r="R43" t="n">
-        <v>6697723</v>
+        <v>6697659</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,9 +5023,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,39 +5050,39 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125717848</v>
+        <v>125718753</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>80106</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5083,17 +5093,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397549</v>
+        <v>397437</v>
       </c>
       <c r="R44" t="n">
-        <v>6697680</v>
+        <v>6697664</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,19 +5130,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,12 +5147,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>125719365</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>125719375</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125719473</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125718932</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>125718708</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>125719337</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>125718537</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>125716840</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718443</v>
+        <v>125719526</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2583,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397480</v>
+        <v>397373</v>
       </c>
       <c r="R19" t="n">
-        <v>6697723</v>
+        <v>6697676</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,9 +2640,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2657,22 +2667,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719526</v>
+        <v>125719134</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2690,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,13 +2714,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397373</v>
+        <v>397331</v>
       </c>
       <c r="R20" t="n">
-        <v>6697676</v>
+        <v>6697672</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,19 +2747,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719134</v>
+        <v>125718443</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,34 +2787,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397331</v>
+        <v>397480</v>
       </c>
       <c r="R21" t="n">
-        <v>6697672</v>
+        <v>6697723</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125718662</v>
+        <v>125718539</v>
       </c>
       <c r="B22" t="n">
-        <v>91248</v>
+        <v>78730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,21 +2884,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397408</v>
+        <v>397411</v>
       </c>
       <c r="R22" t="n">
-        <v>6697666</v>
+        <v>6697715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,45 +2970,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125718539</v>
+        <v>125719694</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>5479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>101920</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397411</v>
+        <v>397212</v>
       </c>
       <c r="R23" t="n">
-        <v>6697715</v>
+        <v>6697719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3070,7 +3075,7 @@
         <v>125717768</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,50 +3179,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125719694</v>
+        <v>125718662</v>
       </c>
       <c r="B25" t="n">
-        <v>5479</v>
+        <v>91252</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101920</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397212</v>
+        <v>397408</v>
       </c>
       <c r="R25" t="n">
-        <v>6697719</v>
+        <v>6697666</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>125718725</v>
       </c>
       <c r="B26" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718601</v>
+        <v>125718584</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397410</v>
+        <v>397396</v>
       </c>
       <c r="R27" t="n">
-        <v>6697671</v>
+        <v>6697692</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,19 +3441,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,44 +3458,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125716739</v>
+        <v>125718195</v>
       </c>
       <c r="B28" t="n">
-        <v>91248</v>
+        <v>75006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397710</v>
+        <v>397560</v>
       </c>
       <c r="R28" t="n">
-        <v>6697735</v>
+        <v>6697723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,45 +3567,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718195</v>
+        <v>125718716</v>
       </c>
       <c r="B29" t="n">
-        <v>75006</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397560</v>
+        <v>397437</v>
       </c>
       <c r="R29" t="n">
-        <v>6697723</v>
+        <v>6697664</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,10 +3664,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718584</v>
+        <v>125718601</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3709,10 +3699,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397396</v>
+        <v>397410</v>
       </c>
       <c r="R30" t="n">
-        <v>6697692</v>
+        <v>6697671</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,9 +3732,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3759,22 +3759,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718716</v>
+        <v>125716739</v>
       </c>
       <c r="B31" t="n">
-        <v>80072</v>
+        <v>91252</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,34 +3782,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397437</v>
+        <v>397710</v>
       </c>
       <c r="R31" t="n">
-        <v>6697664</v>
+        <v>6697735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3871,7 +3871,7 @@
         <v>125718882</v>
       </c>
       <c r="B32" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>125719501</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>125718927</v>
       </c>
       <c r="B36" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>125718597</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>125719141</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718679</v>
+        <v>125718606</v>
       </c>
       <c r="B39" t="n">
-        <v>75006</v>
+        <v>80035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397409</v>
+        <v>397397</v>
       </c>
       <c r="R39" t="n">
-        <v>6697661</v>
+        <v>6697674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125719322</v>
+        <v>125718900</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,13 +4689,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397309</v>
+        <v>397402</v>
       </c>
       <c r="R40" t="n">
-        <v>6697695</v>
+        <v>6697659</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4722,9 +4722,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4739,57 +4749,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718201</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>75006</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397560</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697723</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,10 +4858,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125717848</v>
+        <v>125718201</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4883,13 +4893,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397549</v>
+        <v>397560</v>
       </c>
       <c r="R42" t="n">
-        <v>6697680</v>
+        <v>6697723</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,44 +4943,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718900</v>
+        <v>125718753</v>
       </c>
       <c r="B43" t="n">
-        <v>78635</v>
+        <v>80110</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397402</v>
+        <v>397437</v>
       </c>
       <c r="R43" t="n">
-        <v>6697659</v>
+        <v>6697664</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5023,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,39 +5040,39 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718753</v>
+        <v>125719322</v>
       </c>
       <c r="B44" t="n">
-        <v>80106</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5097,10 +5087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397437</v>
+        <v>397309</v>
       </c>
       <c r="R44" t="n">
-        <v>6697664</v>
+        <v>6697695</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,48 +5149,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718606</v>
+        <v>125717848</v>
       </c>
       <c r="B45" t="n">
-        <v>80031</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397397</v>
+        <v>397549</v>
       </c>
       <c r="R45" t="n">
-        <v>6697674</v>
+        <v>6697680</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,9 +5217,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
         <v>125718531</v>
       </c>
       <c r="B46" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2970,53 +2970,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125719694</v>
+        <v>125717768</v>
       </c>
       <c r="B23" t="n">
-        <v>5479</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397212</v>
+        <v>397538</v>
       </c>
       <c r="R23" t="n">
-        <v>6697719</v>
+        <v>6697682</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3043,9 +3038,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,22 +3065,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125717768</v>
+        <v>125718662</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3083,37 +3088,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397538</v>
+        <v>397408</v>
       </c>
       <c r="R24" t="n">
-        <v>6697682</v>
+        <v>6697666</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3140,19 +3145,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3167,57 +3162,62 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125718662</v>
+        <v>125719694</v>
       </c>
       <c r="B25" t="n">
-        <v>91252</v>
+        <v>5479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397408</v>
+        <v>397212</v>
       </c>
       <c r="R25" t="n">
-        <v>6697666</v>
+        <v>6697719</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R37" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,9 +4421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4438,22 +4448,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,13 +4495,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R38" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,19 +4528,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,22 +4545,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718606</v>
+        <v>125718679</v>
       </c>
       <c r="B39" t="n">
-        <v>80035</v>
+        <v>75006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397397</v>
+        <v>397409</v>
       </c>
       <c r="R39" t="n">
-        <v>6697674</v>
+        <v>6697661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718900</v>
+        <v>125718201</v>
       </c>
       <c r="B40" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4665,37 +4665,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397402</v>
+        <v>397560</v>
       </c>
       <c r="R40" t="n">
-        <v>6697659</v>
+        <v>6697723</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4722,19 +4722,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4749,22 +4739,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125718753</v>
       </c>
       <c r="B41" t="n">
-        <v>75006</v>
+        <v>80110</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,21 +4762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397437</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697664</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718201</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -4889,14 +4879,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397560</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697723</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,27 +4945,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718753</v>
+        <v>125717848</v>
       </c>
       <c r="B43" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4986,17 +4976,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397437</v>
+        <v>397549</v>
       </c>
       <c r="R43" t="n">
-        <v>6697664</v>
+        <v>6697680</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,9 +5013,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,44 +5040,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125719322</v>
+        <v>125718606</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>80035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397309</v>
+        <v>397397</v>
       </c>
       <c r="R44" t="n">
-        <v>6697695</v>
+        <v>6697674</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125717848</v>
+        <v>125718900</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5160,37 +5160,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397549</v>
+        <v>397402</v>
       </c>
       <c r="R45" t="n">
-        <v>6697680</v>
+        <v>6697659</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R47" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,9 +5421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,44 +5448,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>75006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5485,13 +5495,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R48" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5520,7 +5530,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5530,7 +5540,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,60 +5555,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125718722</v>
+        <v>125717791</v>
       </c>
       <c r="B49" t="n">
-        <v>75006</v>
+        <v>79004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397402</v>
+        <v>397585</v>
       </c>
       <c r="R49" t="n">
-        <v>6697659</v>
+        <v>6697687</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5625,19 +5635,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2572,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719526</v>
+        <v>125718443</v>
       </c>
       <c r="B19" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,37 +2583,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>397373</v>
+        <v>397480</v>
       </c>
       <c r="R19" t="n">
-        <v>6697676</v>
+        <v>6697723</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2640,19 +2640,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2667,22 +2657,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719134</v>
+        <v>125719526</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2714,13 +2704,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397331</v>
+        <v>397373</v>
       </c>
       <c r="R20" t="n">
-        <v>6697672</v>
+        <v>6697676</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2747,9 +2737,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718443</v>
+        <v>125719134</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,34 +2787,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397480</v>
+        <v>397331</v>
       </c>
       <c r="R21" t="n">
-        <v>6697723</v>
+        <v>6697672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,45 +3373,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718584</v>
+        <v>125718195</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397396</v>
+        <v>397560</v>
       </c>
       <c r="R27" t="n">
-        <v>6697692</v>
+        <v>6697723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3470,45 +3470,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718195</v>
+        <v>125718716</v>
       </c>
       <c r="B28" t="n">
-        <v>75006</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397560</v>
+        <v>397437</v>
       </c>
       <c r="R28" t="n">
-        <v>6697723</v>
+        <v>6697664</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718716</v>
+        <v>125716739</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,34 +3578,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397437</v>
+        <v>397710</v>
       </c>
       <c r="R29" t="n">
-        <v>6697664</v>
+        <v>6697735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718601</v>
+        <v>125718584</v>
       </c>
       <c r="B30" t="n">
         <v>78972</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397410</v>
+        <v>397396</v>
       </c>
       <c r="R30" t="n">
-        <v>6697671</v>
+        <v>6697692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,19 +3732,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3759,22 +3749,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125716739</v>
+        <v>125718601</v>
       </c>
       <c r="B31" t="n">
-        <v>91252</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,34 +3772,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397710</v>
+        <v>397410</v>
       </c>
       <c r="R31" t="n">
-        <v>6697735</v>
+        <v>6697671</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,9 +3829,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,12 +3856,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718927</v>
+        <v>125718597</v>
       </c>
       <c r="B36" t="n">
-        <v>78639</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397391</v>
+        <v>397397</v>
       </c>
       <c r="R36" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718597</v>
+        <v>125718927</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>78639</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397397</v>
+        <v>397391</v>
       </c>
       <c r="R38" t="n">
-        <v>6697674</v>
+        <v>6697659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>75006</v>
+        <v>78639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R39" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,19 +4652,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718201</v>
+        <v>125719322</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4685,14 +4695,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397560</v>
+        <v>397309</v>
       </c>
       <c r="R40" t="n">
-        <v>6697723</v>
+        <v>6697695</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,27 +4761,27 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718753</v>
+        <v>125718201</v>
       </c>
       <c r="B41" t="n">
-        <v>80110</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4782,14 +4792,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397437</v>
+        <v>397560</v>
       </c>
       <c r="R41" t="n">
-        <v>6697664</v>
+        <v>6697723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125719322</v>
+        <v>125717848</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -4879,17 +4889,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397309</v>
+        <v>397549</v>
       </c>
       <c r="R42" t="n">
-        <v>6697695</v>
+        <v>6697680</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,9 +4926,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4933,60 +4953,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125717848</v>
+        <v>125718679</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>75006</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397549</v>
+        <v>397409</v>
       </c>
       <c r="R43" t="n">
-        <v>6697680</v>
+        <v>6697661</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5013,19 +5033,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718606</v>
+        <v>125718753</v>
       </c>
       <c r="B44" t="n">
-        <v>80035</v>
+        <v>80110</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5087,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397397</v>
+        <v>397437</v>
       </c>
       <c r="R44" t="n">
-        <v>6697674</v>
+        <v>6697664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5149,32 +5159,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718900</v>
+        <v>125718606</v>
       </c>
       <c r="B45" t="n">
-        <v>78639</v>
+        <v>80035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5184,13 +5194,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397402</v>
+        <v>397397</v>
       </c>
       <c r="R45" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5217,19 +5227,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125719487</v>
+        <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397214</v>
+        <v>397585</v>
       </c>
       <c r="R47" t="n">
-        <v>6697663</v>
+        <v>6697687</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,19 +5421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,44 +5438,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125718722</v>
+        <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>75006</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5495,13 +5485,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397402</v>
+        <v>397214</v>
       </c>
       <c r="R48" t="n">
-        <v>6697659</v>
+        <v>6697663</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5530,7 +5520,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5540,7 +5530,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5555,60 +5545,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125717791</v>
+        <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>75006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397585</v>
+        <v>397402</v>
       </c>
       <c r="R49" t="n">
-        <v>6697687</v>
+        <v>6697659</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5635,9 +5625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718900</v>
+        <v>125719322</v>
       </c>
       <c r="B39" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397402</v>
+        <v>397309</v>
       </c>
       <c r="R39" t="n">
-        <v>6697659</v>
+        <v>6697695</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,19 +4625,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,19 +4642,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125719322</v>
+        <v>125718201</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4695,14 +4685,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397309</v>
+        <v>397560</v>
       </c>
       <c r="R40" t="n">
-        <v>6697695</v>
+        <v>6697723</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,7 +4751,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718201</v>
+        <v>125717848</v>
       </c>
       <c r="B41" t="n">
         <v>78972</v>
@@ -4796,13 +4786,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397560</v>
+        <v>397549</v>
       </c>
       <c r="R41" t="n">
-        <v>6697723</v>
+        <v>6697680</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4829,9 +4819,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,60 +4846,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125717848</v>
+        <v>125718606</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>80035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397549</v>
+        <v>397397</v>
       </c>
       <c r="R42" t="n">
-        <v>6697680</v>
+        <v>6697674</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,19 +4926,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4953,44 +4943,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B43" t="n">
-        <v>75006</v>
+        <v>78639</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5000,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R43" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,9 +5023,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,22 +5050,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718753</v>
+        <v>125718679</v>
       </c>
       <c r="B44" t="n">
-        <v>80110</v>
+        <v>75006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397437</v>
+        <v>397409</v>
       </c>
       <c r="R44" t="n">
-        <v>6697664</v>
+        <v>6697661</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,10 +5159,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718606</v>
+        <v>125718753</v>
       </c>
       <c r="B45" t="n">
-        <v>80035</v>
+        <v>80110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5170,21 +5170,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397397</v>
+        <v>397437</v>
       </c>
       <c r="R45" t="n">
-        <v>6697674</v>
+        <v>6697664</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>80075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R47" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,9 +5421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,44 +5448,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>75006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5485,13 +5495,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R48" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5520,7 +5530,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5530,7 +5540,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,60 +5555,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125718722</v>
+        <v>125717791</v>
       </c>
       <c r="B49" t="n">
-        <v>75006</v>
+        <v>79004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397402</v>
+        <v>397585</v>
       </c>
       <c r="R49" t="n">
-        <v>6697659</v>
+        <v>6697687</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5625,19 +5635,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -3373,45 +3373,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718195</v>
+        <v>125718601</v>
       </c>
       <c r="B27" t="n">
-        <v>75006</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397560</v>
+        <v>397410</v>
       </c>
       <c r="R27" t="n">
-        <v>6697723</v>
+        <v>6697671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,9 +3441,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,57 +3468,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718716</v>
+        <v>125718195</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>75006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397437</v>
+        <v>397560</v>
       </c>
       <c r="R28" t="n">
-        <v>6697664</v>
+        <v>6697723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125716739</v>
+        <v>125718716</v>
       </c>
       <c r="B29" t="n">
-        <v>91252</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,34 +3588,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397710</v>
+        <v>397437</v>
       </c>
       <c r="R29" t="n">
-        <v>6697735</v>
+        <v>6697664</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3664,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718584</v>
+        <v>125716739</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3675,34 +3685,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397396</v>
+        <v>397710</v>
       </c>
       <c r="R30" t="n">
-        <v>6697692</v>
+        <v>6697735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3761,7 +3771,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718601</v>
+        <v>125718584</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3796,10 +3806,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397410</v>
+        <v>397396</v>
       </c>
       <c r="R31" t="n">
-        <v>6697671</v>
+        <v>6697692</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3829,19 +3839,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,12 +3856,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718597</v>
+        <v>125718927</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>78639</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397397</v>
+        <v>397391</v>
       </c>
       <c r="R36" t="n">
-        <v>6697674</v>
+        <v>6697659</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R37" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,19 +4421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4448,22 +4438,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718927</v>
+        <v>125719141</v>
       </c>
       <c r="B38" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,13 +4485,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397391</v>
+        <v>397373</v>
       </c>
       <c r="R38" t="n">
-        <v>6697659</v>
+        <v>6697657</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4528,9 +4518,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,12 +4545,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125719487</v>
+        <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>79004</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397214</v>
+        <v>397585</v>
       </c>
       <c r="R47" t="n">
-        <v>6697663</v>
+        <v>6697687</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,19 +5421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,44 +5438,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125718722</v>
+        <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>75006</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5495,13 +5485,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397402</v>
+        <v>397214</v>
       </c>
       <c r="R48" t="n">
-        <v>6697659</v>
+        <v>6697663</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5530,7 +5520,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5540,7 +5530,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5555,60 +5545,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125717791</v>
+        <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>79004</v>
+        <v>75006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397585</v>
+        <v>397402</v>
       </c>
       <c r="R49" t="n">
-        <v>6697687</v>
+        <v>6697659</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5635,9 +5625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>125719365</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>125719375</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125719473</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125718932</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>125718708</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>125719337</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>125718537</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>125716840</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>125718443</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>125719526</v>
       </c>
       <c r="B20" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>125719134</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>125718539</v>
       </c>
       <c r="B22" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>125717768</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>125718662</v>
       </c>
       <c r="B24" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>125718725</v>
       </c>
       <c r="B26" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,45 +3373,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718601</v>
+        <v>125718195</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>75007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397410</v>
+        <v>397560</v>
       </c>
       <c r="R27" t="n">
-        <v>6697671</v>
+        <v>6697723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,19 +3441,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,57 +3458,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718195</v>
+        <v>125718601</v>
       </c>
       <c r="B28" t="n">
-        <v>75006</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397560</v>
+        <v>397410</v>
       </c>
       <c r="R28" t="n">
-        <v>6697723</v>
+        <v>6697671</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,9 +3538,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,12 +3565,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3580,7 +3580,7 @@
         <v>125718716</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>125716739</v>
       </c>
       <c r="B30" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>125718584</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>125718882</v>
       </c>
       <c r="B32" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>125717751</v>
       </c>
       <c r="B33" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>125719501</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>125718927</v>
       </c>
       <c r="B36" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R37" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,9 +4421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4438,22 +4448,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,13 +4495,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R38" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,19 +4528,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,44 +4545,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125719322</v>
+        <v>125718606</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>80036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397309</v>
+        <v>397397</v>
       </c>
       <c r="R39" t="n">
-        <v>6697695</v>
+        <v>6697674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,27 +4654,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718201</v>
+        <v>125718753</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>80111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4685,14 +4685,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397560</v>
+        <v>397437</v>
       </c>
       <c r="R40" t="n">
-        <v>6697723</v>
+        <v>6697664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,48 +4751,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125717848</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>75007</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397549</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697680</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4819,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,44 +4836,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718606</v>
+        <v>125718900</v>
       </c>
       <c r="B42" t="n">
-        <v>80035</v>
+        <v>78640</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4893,13 +4883,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397397</v>
+        <v>397402</v>
       </c>
       <c r="R42" t="n">
-        <v>6697674</v>
+        <v>6697659</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,9 +4916,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,22 +4943,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718900</v>
+        <v>125719322</v>
       </c>
       <c r="B43" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,21 +4966,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397402</v>
+        <v>397309</v>
       </c>
       <c r="R43" t="n">
-        <v>6697659</v>
+        <v>6697695</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5023,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,57 +5040,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718679</v>
+        <v>125718201</v>
       </c>
       <c r="B44" t="n">
-        <v>75006</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397409</v>
+        <v>397560</v>
       </c>
       <c r="R44" t="n">
-        <v>6697661</v>
+        <v>6697723</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,27 +5149,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718753</v>
+        <v>125717848</v>
       </c>
       <c r="B45" t="n">
-        <v>80110</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5190,17 +5180,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397437</v>
+        <v>397549</v>
       </c>
       <c r="R45" t="n">
-        <v>6697664</v>
+        <v>6697680</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,9 +5217,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
         <v>125718531</v>
       </c>
       <c r="B46" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>125718062</v>
       </c>
       <c r="B50" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718927</v>
+        <v>125719141</v>
       </c>
       <c r="B36" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397391</v>
+        <v>397373</v>
       </c>
       <c r="R36" t="n">
-        <v>6697659</v>
+        <v>6697657</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4324,9 +4324,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4341,22 +4351,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125719141</v>
+        <v>125718927</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4374,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4398,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397373</v>
+        <v>397391</v>
       </c>
       <c r="R37" t="n">
-        <v>6697657</v>
+        <v>6697659</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,19 +4431,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4448,12 +4448,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2873,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125718539</v>
+        <v>125718662</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>91256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,21 +2884,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397411</v>
+        <v>397408</v>
       </c>
       <c r="R22" t="n">
-        <v>6697715</v>
+        <v>6697666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125717768</v>
+        <v>125718539</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,37 +2981,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397538</v>
+        <v>397411</v>
       </c>
       <c r="R23" t="n">
-        <v>6697682</v>
+        <v>6697715</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3038,19 +3038,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,22 +3055,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125718662</v>
+        <v>125717768</v>
       </c>
       <c r="B24" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,37 +3078,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397408</v>
+        <v>397538</v>
       </c>
       <c r="R24" t="n">
-        <v>6697666</v>
+        <v>6697682</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3145,9 +3135,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,12 +3162,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3373,45 +3373,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718195</v>
+        <v>125718601</v>
       </c>
       <c r="B27" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397560</v>
+        <v>397410</v>
       </c>
       <c r="R27" t="n">
-        <v>6697723</v>
+        <v>6697671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,9 +3441,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,22 +3468,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718601</v>
+        <v>125718716</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3505,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397410</v>
+        <v>397437</v>
       </c>
       <c r="R28" t="n">
-        <v>6697671</v>
+        <v>6697664</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3538,19 +3548,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,22 +3565,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718716</v>
+        <v>125716739</v>
       </c>
       <c r="B29" t="n">
-        <v>80077</v>
+        <v>91256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,34 +3588,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397437</v>
+        <v>397710</v>
       </c>
       <c r="R29" t="n">
-        <v>6697664</v>
+        <v>6697735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125716739</v>
+        <v>125718584</v>
       </c>
       <c r="B30" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3685,34 +3685,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397710</v>
+        <v>397396</v>
       </c>
       <c r="R30" t="n">
-        <v>6697735</v>
+        <v>6697692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,45 +3771,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718584</v>
+        <v>125718195</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397396</v>
+        <v>397560</v>
       </c>
       <c r="R31" t="n">
-        <v>6697692</v>
+        <v>6697723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R36" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4324,19 +4324,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4351,12 +4341,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4460,10 +4450,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,13 +4485,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R38" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4528,9 +4518,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,22 +4545,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718606</v>
+        <v>125718679</v>
       </c>
       <c r="B39" t="n">
-        <v>80036</v>
+        <v>75007</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397397</v>
+        <v>397409</v>
       </c>
       <c r="R39" t="n">
-        <v>6697674</v>
+        <v>6697661</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,27 +4654,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718753</v>
+        <v>125719322</v>
       </c>
       <c r="B40" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397437</v>
+        <v>397309</v>
       </c>
       <c r="R40" t="n">
-        <v>6697664</v>
+        <v>6697695</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,45 +4751,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125718201</v>
       </c>
       <c r="B41" t="n">
-        <v>75007</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397560</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718900</v>
+        <v>125717848</v>
       </c>
       <c r="B42" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,37 +4859,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397402</v>
+        <v>397549</v>
       </c>
       <c r="R42" t="n">
-        <v>6697659</v>
+        <v>6697680</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,39 +4943,39 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125719322</v>
+        <v>125718753</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397309</v>
+        <v>397437</v>
       </c>
       <c r="R43" t="n">
-        <v>6697695</v>
+        <v>6697664</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718201</v>
+        <v>125718900</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,37 +5063,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397560</v>
+        <v>397402</v>
       </c>
       <c r="R44" t="n">
-        <v>6697723</v>
+        <v>6697659</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,9 +5120,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,60 +5147,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125717848</v>
+        <v>125718606</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>80036</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397549</v>
+        <v>397397</v>
       </c>
       <c r="R45" t="n">
-        <v>6697680</v>
+        <v>6697674</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5217,19 +5227,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B47" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R47" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,9 +5421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,44 +5448,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B48" t="n">
-        <v>80076</v>
+        <v>75007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5485,13 +5495,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R48" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5520,7 +5530,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5530,7 +5540,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,60 +5555,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125718722</v>
+        <v>125717791</v>
       </c>
       <c r="B49" t="n">
-        <v>75007</v>
+        <v>79005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397402</v>
+        <v>397585</v>
       </c>
       <c r="R49" t="n">
-        <v>6697659</v>
+        <v>6697687</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5625,19 +5635,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1726,7 +1726,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125719365</v>
+        <v>125719375</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397373</v>
+        <v>397295</v>
       </c>
       <c r="R11" t="n">
-        <v>6697676</v>
+        <v>6697668</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,19 +1821,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125719375</v>
+        <v>125719365</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397295</v>
+        <v>397373</v>
       </c>
       <c r="R12" t="n">
-        <v>6697668</v>
+        <v>6697676</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,12 +1928,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -4557,32 +4557,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>75007</v>
+        <v>78640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R39" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,44 +4652,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125719322</v>
+        <v>125718606</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>80036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397309</v>
+        <v>397397</v>
       </c>
       <c r="R40" t="n">
-        <v>6697695</v>
+        <v>6697674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,45 +4761,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718201</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397560</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697723</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125717848</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4879,17 +4889,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397549</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697680</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,19 +4926,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4943,39 +4943,39 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718753</v>
+        <v>125718201</v>
       </c>
       <c r="B43" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4986,14 +4986,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397437</v>
+        <v>397560</v>
       </c>
       <c r="R43" t="n">
-        <v>6697664</v>
+        <v>6697723</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718900</v>
+        <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,37 +5063,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397402</v>
+        <v>397549</v>
       </c>
       <c r="R44" t="n">
-        <v>6697659</v>
+        <v>6697680</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,22 +5147,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718606</v>
+        <v>125718753</v>
       </c>
       <c r="B45" t="n">
-        <v>80036</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5170,21 +5170,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397397</v>
+        <v>397437</v>
       </c>
       <c r="R45" t="n">
-        <v>6697674</v>
+        <v>6697664</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1726,7 +1726,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125719375</v>
+        <v>125719365</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>397295</v>
+        <v>397373</v>
       </c>
       <c r="R11" t="n">
-        <v>6697668</v>
+        <v>6697676</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,19 +1821,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125719365</v>
+        <v>125719375</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>397373</v>
+        <v>397295</v>
       </c>
       <c r="R12" t="n">
-        <v>6697676</v>
+        <v>6697668</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,12 +1928,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125719337</v>
+        <v>125718537</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397294</v>
+        <v>397396</v>
       </c>
       <c r="R16" t="n">
-        <v>6697669</v>
+        <v>6697728</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125718537</v>
+        <v>125716840</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2399,17 +2399,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397396</v>
+        <v>397730</v>
       </c>
       <c r="R17" t="n">
-        <v>6697728</v>
+        <v>6697688</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,19 +2436,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,19 +2453,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125716840</v>
+        <v>125719337</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2506,17 +2496,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397730</v>
+        <v>397294</v>
       </c>
       <c r="R18" t="n">
-        <v>6697688</v>
+        <v>6697669</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2543,9 +2533,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,12 +2560,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719526</v>
+        <v>125719134</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397373</v>
+        <v>397331</v>
       </c>
       <c r="R20" t="n">
-        <v>6697676</v>
+        <v>6697672</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,19 +2737,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,22 +2754,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719134</v>
+        <v>125719526</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2787,21 +2777,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2811,13 +2801,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397331</v>
+        <v>397373</v>
       </c>
       <c r="R21" t="n">
-        <v>6697672</v>
+        <v>6697676</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2844,9 +2834,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,22 +2861,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125718662</v>
+        <v>125717768</v>
       </c>
       <c r="B22" t="n">
-        <v>91256</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,37 +2884,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397408</v>
+        <v>397538</v>
       </c>
       <c r="R22" t="n">
-        <v>6697666</v>
+        <v>6697682</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2941,9 +2941,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,22 +2968,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125718539</v>
+        <v>125718662</v>
       </c>
       <c r="B23" t="n">
-        <v>78731</v>
+        <v>91258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,21 +2991,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3005,10 +3015,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397411</v>
+        <v>397408</v>
       </c>
       <c r="R23" t="n">
-        <v>6697715</v>
+        <v>6697666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,48 +3077,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125717768</v>
+        <v>125719694</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>5479</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397538</v>
+        <v>397212</v>
       </c>
       <c r="R24" t="n">
-        <v>6697682</v>
+        <v>6697719</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3135,19 +3150,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3162,62 +3167,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125719694</v>
+        <v>125718539</v>
       </c>
       <c r="B25" t="n">
-        <v>5479</v>
+        <v>78731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101920</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397212</v>
+        <v>397411</v>
       </c>
       <c r="R25" t="n">
-        <v>6697719</v>
+        <v>6697715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718601</v>
+        <v>125718716</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397410</v>
+        <v>397437</v>
       </c>
       <c r="R27" t="n">
-        <v>6697671</v>
+        <v>6697664</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,19 +3441,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,22 +3458,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718716</v>
+        <v>125718584</v>
       </c>
       <c r="B28" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3481,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397437</v>
+        <v>397396</v>
       </c>
       <c r="R28" t="n">
-        <v>6697664</v>
+        <v>6697692</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3577,10 +3567,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125716739</v>
+        <v>125718601</v>
       </c>
       <c r="B29" t="n">
-        <v>91256</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,34 +3578,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397710</v>
+        <v>397410</v>
       </c>
       <c r="R29" t="n">
-        <v>6697735</v>
+        <v>6697671</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,9 +3635,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,22 +3662,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718584</v>
+        <v>125716739</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>91258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3685,34 +3685,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397396</v>
+        <v>397710</v>
       </c>
       <c r="R30" t="n">
-        <v>6697692</v>
+        <v>6697735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125718882</v>
+        <v>125717751</v>
       </c>
       <c r="B32" t="n">
-        <v>80105</v>
+        <v>75007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,34 +3879,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397437</v>
+        <v>397590</v>
       </c>
       <c r="R32" t="n">
-        <v>6697664</v>
+        <v>6697690</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125717751</v>
+        <v>125718882</v>
       </c>
       <c r="B33" t="n">
-        <v>75007</v>
+        <v>80105</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,34 +3976,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397590</v>
+        <v>397437</v>
       </c>
       <c r="R33" t="n">
-        <v>6697690</v>
+        <v>6697664</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R36" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4324,9 +4324,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4341,12 +4351,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4450,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4461,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,13 +4495,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R38" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,19 +4528,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,22 +4545,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718900</v>
+        <v>125719322</v>
       </c>
       <c r="B39" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397402</v>
+        <v>397309</v>
       </c>
       <c r="R39" t="n">
-        <v>6697659</v>
+        <v>6697695</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,19 +4625,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,22 +4642,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718606</v>
+        <v>125718753</v>
       </c>
       <c r="B40" t="n">
-        <v>80036</v>
+        <v>80111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,21 +4665,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397397</v>
+        <v>397437</v>
       </c>
       <c r="R40" t="n">
-        <v>6697674</v>
+        <v>6697664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125718606</v>
       </c>
       <c r="B41" t="n">
-        <v>75007</v>
+        <v>80036</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4772,21 +4762,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397397</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125719322</v>
+        <v>125718201</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4889,14 +4879,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397309</v>
+        <v>397560</v>
       </c>
       <c r="R42" t="n">
-        <v>6697695</v>
+        <v>6697723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,10 +4945,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718201</v>
+        <v>125718900</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4966,37 +4956,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397560</v>
+        <v>397402</v>
       </c>
       <c r="R43" t="n">
-        <v>6697723</v>
+        <v>6697659</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,9 +5013,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,60 +5040,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125717848</v>
+        <v>125718679</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>75007</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397549</v>
+        <v>397409</v>
       </c>
       <c r="R44" t="n">
-        <v>6697680</v>
+        <v>6697661</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,19 +5120,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,39 +5137,39 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718753</v>
+        <v>125717848</v>
       </c>
       <c r="B45" t="n">
-        <v>80111</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5190,17 +5180,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397437</v>
+        <v>397549</v>
       </c>
       <c r="R45" t="n">
-        <v>6697664</v>
+        <v>6697680</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,9 +5217,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125719487</v>
+        <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>79005</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397214</v>
+        <v>397585</v>
       </c>
       <c r="R47" t="n">
-        <v>6697663</v>
+        <v>6697687</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,19 +5421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,12 +5438,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5567,10 +5557,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B49" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5578,37 +5568,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R49" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5635,9 +5625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125719134</v>
+        <v>125719526</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,21 +2680,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>397331</v>
+        <v>397373</v>
       </c>
       <c r="R20" t="n">
-        <v>6697672</v>
+        <v>6697676</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2737,9 +2737,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2754,22 +2764,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719526</v>
+        <v>125719134</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,21 +2787,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2801,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>397373</v>
+        <v>397331</v>
       </c>
       <c r="R21" t="n">
-        <v>6697676</v>
+        <v>6697672</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2834,19 +2844,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2861,12 +2861,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125719322</v>
+        <v>125718201</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4588,14 +4588,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397309</v>
+        <v>397560</v>
       </c>
       <c r="R39" t="n">
-        <v>6697695</v>
+        <v>6697723</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,10 +4654,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718753</v>
+        <v>125718679</v>
       </c>
       <c r="B40" t="n">
-        <v>80111</v>
+        <v>75007</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4665,21 +4665,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397437</v>
+        <v>397409</v>
       </c>
       <c r="R40" t="n">
-        <v>6697664</v>
+        <v>6697661</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,48 +4751,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718606</v>
+        <v>125717848</v>
       </c>
       <c r="B41" t="n">
-        <v>80036</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397397</v>
+        <v>397549</v>
       </c>
       <c r="R41" t="n">
-        <v>6697674</v>
+        <v>6697680</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,9 +4819,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4836,19 +4846,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718201</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4879,14 +4889,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397560</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697723</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,32 +4955,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718900</v>
+        <v>125718606</v>
       </c>
       <c r="B43" t="n">
-        <v>78640</v>
+        <v>80036</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4980,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397402</v>
+        <v>397397</v>
       </c>
       <c r="R43" t="n">
-        <v>6697659</v>
+        <v>6697674</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5013,19 +5023,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,44 +5040,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B44" t="n">
-        <v>75007</v>
+        <v>78640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R44" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,9 +5120,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5137,39 +5147,39 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125717848</v>
+        <v>125718753</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>80111</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5180,17 +5190,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397549</v>
+        <v>397437</v>
       </c>
       <c r="R45" t="n">
-        <v>6697680</v>
+        <v>6697664</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5217,19 +5227,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5244,12 +5244,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125717791</v>
+        <v>125719487</v>
       </c>
       <c r="B47" t="n">
-        <v>79005</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397585</v>
+        <v>397214</v>
       </c>
       <c r="R47" t="n">
-        <v>6697687</v>
+        <v>6697663</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,9 +5421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5438,60 +5448,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125718722</v>
+        <v>125717791</v>
       </c>
       <c r="B48" t="n">
-        <v>75007</v>
+        <v>79005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397402</v>
+        <v>397585</v>
       </c>
       <c r="R48" t="n">
-        <v>6697659</v>
+        <v>6697687</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5518,19 +5528,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,44 +5545,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>80076</v>
+        <v>75007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5592,13 +5592,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R49" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>125719365</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>125719375</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>125719473</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>125718932</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>125718708</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125718537</v>
+        <v>125719337</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>397396</v>
+        <v>397294</v>
       </c>
       <c r="R16" t="n">
-        <v>6697728</v>
+        <v>6697669</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125716840</v>
+        <v>125718537</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,17 +2399,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>397730</v>
+        <v>397396</v>
       </c>
       <c r="R17" t="n">
-        <v>6697688</v>
+        <v>6697728</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2436,9 +2436,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2453,22 +2463,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125719337</v>
+        <v>125716840</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,17 +2506,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>397294</v>
+        <v>397730</v>
       </c>
       <c r="R18" t="n">
-        <v>6697669</v>
+        <v>6697688</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,19 +2543,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,12 +2560,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
         <v>125718443</v>
       </c>
       <c r="B19" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>125719526</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>125719134</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>125717768</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>125718662</v>
       </c>
       <c r="B23" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,50 +3077,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125719694</v>
+        <v>125718539</v>
       </c>
       <c r="B24" t="n">
-        <v>5479</v>
+        <v>78735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101920</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397212</v>
+        <v>397411</v>
       </c>
       <c r="R24" t="n">
-        <v>6697719</v>
+        <v>6697715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3179,45 +3174,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125718539</v>
+        <v>125719694</v>
       </c>
       <c r="B25" t="n">
-        <v>78731</v>
+        <v>5479</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>101920</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>397411</v>
+        <v>397212</v>
       </c>
       <c r="R25" t="n">
-        <v>6697715</v>
+        <v>6697719</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,7 +3279,7 @@
         <v>125718725</v>
       </c>
       <c r="B26" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718716</v>
+        <v>125718601</v>
       </c>
       <c r="B27" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397437</v>
+        <v>397410</v>
       </c>
       <c r="R27" t="n">
-        <v>6697664</v>
+        <v>6697671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,9 +3441,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3458,22 +3468,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125718584</v>
+        <v>125716739</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>91262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3481,34 +3491,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397396</v>
+        <v>397710</v>
       </c>
       <c r="R28" t="n">
-        <v>6697692</v>
+        <v>6697735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,10 +3577,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718601</v>
+        <v>125718584</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397410</v>
+        <v>397396</v>
       </c>
       <c r="R29" t="n">
-        <v>6697671</v>
+        <v>6697692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3635,19 +3645,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,44 +3662,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125716739</v>
+        <v>125718195</v>
       </c>
       <c r="B30" t="n">
-        <v>91258</v>
+        <v>75011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397710</v>
+        <v>397560</v>
       </c>
       <c r="R30" t="n">
-        <v>6697735</v>
+        <v>6697723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,45 +3771,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718195</v>
+        <v>125718716</v>
       </c>
       <c r="B31" t="n">
-        <v>75007</v>
+        <v>80081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397560</v>
+        <v>397437</v>
       </c>
       <c r="R31" t="n">
-        <v>6697723</v>
+        <v>6697664</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125717751</v>
+        <v>125718882</v>
       </c>
       <c r="B32" t="n">
-        <v>75007</v>
+        <v>80109</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,34 +3879,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397590</v>
+        <v>397437</v>
       </c>
       <c r="R32" t="n">
-        <v>6697690</v>
+        <v>6697664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125718882</v>
+        <v>125717751</v>
       </c>
       <c r="B33" t="n">
-        <v>80105</v>
+        <v>75011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,34 +3976,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397437</v>
+        <v>397590</v>
       </c>
       <c r="R33" t="n">
-        <v>6697664</v>
+        <v>6697690</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,7 +4065,7 @@
         <v>125719501</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>125719032</v>
       </c>
       <c r="B35" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125719141</v>
+        <v>125718927</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4267,21 +4267,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>397373</v>
+        <v>397391</v>
       </c>
       <c r="R36" t="n">
-        <v>6697657</v>
+        <v>6697659</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4324,19 +4324,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4351,22 +4341,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125718927</v>
+        <v>125719141</v>
       </c>
       <c r="B37" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4374,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397391</v>
+        <v>397373</v>
       </c>
       <c r="R37" t="n">
-        <v>6697659</v>
+        <v>6697657</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4431,9 +4421,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4448,12 +4448,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4463,7 +4463,7 @@
         <v>125718597</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718201</v>
+        <v>125718900</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397560</v>
+        <v>397402</v>
       </c>
       <c r="R39" t="n">
-        <v>6697723</v>
+        <v>6697659</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4625,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,22 +4652,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718679</v>
+        <v>125718753</v>
       </c>
       <c r="B40" t="n">
-        <v>75007</v>
+        <v>80115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4665,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397409</v>
+        <v>397437</v>
       </c>
       <c r="R40" t="n">
-        <v>6697661</v>
+        <v>6697664</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4751,48 +4761,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125717848</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>75011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397549</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697680</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4819,19 +4829,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4846,12 +4846,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4861,7 +4861,7 @@
         <v>125719322</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4955,45 +4955,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718606</v>
+        <v>125718201</v>
       </c>
       <c r="B43" t="n">
-        <v>80036</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397397</v>
+        <v>397560</v>
       </c>
       <c r="R43" t="n">
-        <v>6697674</v>
+        <v>6697723</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718900</v>
+        <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,37 +5063,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397402</v>
+        <v>397549</v>
       </c>
       <c r="R44" t="n">
-        <v>6697659</v>
+        <v>6697680</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,22 +5147,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125718753</v>
+        <v>125718606</v>
       </c>
       <c r="B45" t="n">
-        <v>80111</v>
+        <v>80040</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5170,21 +5170,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>397437</v>
+        <v>397397</v>
       </c>
       <c r="R45" t="n">
-        <v>6697664</v>
+        <v>6697674</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5259,7 +5259,7 @@
         <v>125718531</v>
       </c>
       <c r="B46" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125719487</v>
+        <v>125717791</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>79009</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5364,37 +5364,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>397214</v>
+        <v>397585</v>
       </c>
       <c r="R47" t="n">
-        <v>6697663</v>
+        <v>6697687</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5421,19 +5421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,60 +5438,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125717791</v>
+        <v>125718722</v>
       </c>
       <c r="B48" t="n">
-        <v>79005</v>
+        <v>75011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397585</v>
+        <v>397402</v>
       </c>
       <c r="R48" t="n">
-        <v>6697687</v>
+        <v>6697659</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5528,9 +5518,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,44 +5545,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125718722</v>
+        <v>125719487</v>
       </c>
       <c r="B49" t="n">
-        <v>75007</v>
+        <v>80080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5592,13 +5592,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397402</v>
+        <v>397214</v>
       </c>
       <c r="R49" t="n">
-        <v>6697659</v>
+        <v>6697663</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5667,7 +5667,7 @@
         <v>125718062</v>
       </c>
       <c r="B50" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125718601</v>
+        <v>125718716</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>397410</v>
+        <v>397437</v>
       </c>
       <c r="R27" t="n">
-        <v>6697671</v>
+        <v>6697664</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,19 +3441,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3468,22 +3458,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125716739</v>
+        <v>125718601</v>
       </c>
       <c r="B28" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,34 +3481,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>397710</v>
+        <v>397410</v>
       </c>
       <c r="R28" t="n">
-        <v>6697735</v>
+        <v>6697671</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,9 +3538,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3565,22 +3565,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125718584</v>
+        <v>125716739</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3588,34 +3588,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>397396</v>
+        <v>397710</v>
       </c>
       <c r="R29" t="n">
-        <v>6697692</v>
+        <v>6697735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3674,45 +3674,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125718195</v>
+        <v>125718584</v>
       </c>
       <c r="B30" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>397560</v>
+        <v>397396</v>
       </c>
       <c r="R30" t="n">
-        <v>6697723</v>
+        <v>6697692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,45 +3771,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125718716</v>
+        <v>125718195</v>
       </c>
       <c r="B31" t="n">
-        <v>80081</v>
+        <v>75011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>397437</v>
+        <v>397560</v>
       </c>
       <c r="R31" t="n">
-        <v>6697664</v>
+        <v>6697723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125718882</v>
+        <v>125717751</v>
       </c>
       <c r="B32" t="n">
-        <v>80109</v>
+        <v>75011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,34 +3879,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>397437</v>
+        <v>397590</v>
       </c>
       <c r="R32" t="n">
-        <v>6697664</v>
+        <v>6697690</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125717751</v>
+        <v>125718882</v>
       </c>
       <c r="B33" t="n">
-        <v>75011</v>
+        <v>80109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3976,34 +3976,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>397590</v>
+        <v>397437</v>
       </c>
       <c r="R33" t="n">
-        <v>6697690</v>
+        <v>6697664</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -2873,10 +2873,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125717768</v>
+        <v>125718539</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,37 +2884,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>397538</v>
+        <v>397411</v>
       </c>
       <c r="R22" t="n">
-        <v>6697682</v>
+        <v>6697715</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2941,19 +2941,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2968,22 +2958,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125718662</v>
+        <v>125717768</v>
       </c>
       <c r="B23" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2991,37 +2981,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>397408</v>
+        <v>397538</v>
       </c>
       <c r="R23" t="n">
-        <v>6697666</v>
+        <v>6697682</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3048,9 +3038,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,22 +3065,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125718539</v>
+        <v>125718662</v>
       </c>
       <c r="B24" t="n">
-        <v>78735</v>
+        <v>91262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,21 +3088,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>397411</v>
+        <v>397408</v>
       </c>
       <c r="R24" t="n">
-        <v>6697715</v>
+        <v>6697666</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125719141</v>
+        <v>125718597</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,21 +4364,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>397373</v>
+        <v>397397</v>
       </c>
       <c r="R37" t="n">
-        <v>6697657</v>
+        <v>6697674</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,19 +4421,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4448,22 +4438,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125718597</v>
+        <v>125719141</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4471,21 +4461,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,13 +4485,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>397397</v>
+        <v>397373</v>
       </c>
       <c r="R38" t="n">
-        <v>6697674</v>
+        <v>6697657</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4528,9 +4518,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4545,12 +4545,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718753</v>
+        <v>125718679</v>
       </c>
       <c r="B40" t="n">
-        <v>80115</v>
+        <v>75011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397437</v>
+        <v>397409</v>
       </c>
       <c r="R40" t="n">
-        <v>6697664</v>
+        <v>6697661</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4761,32 +4761,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125718679</v>
+        <v>125719322</v>
       </c>
       <c r="B41" t="n">
-        <v>75011</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397409</v>
+        <v>397309</v>
       </c>
       <c r="R41" t="n">
-        <v>6697661</v>
+        <v>6697695</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125719322</v>
+        <v>125718201</v>
       </c>
       <c r="B42" t="n">
         <v>78977</v>
@@ -4889,14 +4889,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397309</v>
+        <v>397560</v>
       </c>
       <c r="R42" t="n">
-        <v>6697695</v>
+        <v>6697723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125718201</v>
+        <v>125717848</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397560</v>
+        <v>397549</v>
       </c>
       <c r="R43" t="n">
-        <v>6697723</v>
+        <v>6697680</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,9 +5023,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5040,39 +5050,39 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125717848</v>
+        <v>125718753</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>80115</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5083,17 +5093,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397549</v>
+        <v>397437</v>
       </c>
       <c r="R44" t="n">
-        <v>6697680</v>
+        <v>6697664</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5120,19 +5130,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,12 +5147,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5450,32 +5450,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125718722</v>
+        <v>125719487</v>
       </c>
       <c r="B48" t="n">
-        <v>75011</v>
+        <v>80080</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5485,13 +5485,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>397402</v>
+        <v>397214</v>
       </c>
       <c r="R48" t="n">
-        <v>6697659</v>
+        <v>6697663</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5545,44 +5545,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125719487</v>
+        <v>125718722</v>
       </c>
       <c r="B49" t="n">
-        <v>80080</v>
+        <v>75011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5592,13 +5592,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>397214</v>
+        <v>397402</v>
       </c>
       <c r="R49" t="n">
-        <v>6697663</v>
+        <v>6697659</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5652,12 +5652,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 45814-2024 artfynd.xlsx
+++ b/artfynd/A 45814-2024 artfynd.xlsx
@@ -4557,32 +4557,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125718900</v>
+        <v>125718753</v>
       </c>
       <c r="B39" t="n">
-        <v>78644</v>
+        <v>80115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>397402</v>
+        <v>397437</v>
       </c>
       <c r="R39" t="n">
-        <v>6697659</v>
+        <v>6697664</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,19 +4625,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4652,44 +4642,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125718679</v>
+        <v>125718900</v>
       </c>
       <c r="B40" t="n">
-        <v>75011</v>
+        <v>78644</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4699,13 +4689,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>397409</v>
+        <v>397402</v>
       </c>
       <c r="R40" t="n">
-        <v>6697661</v>
+        <v>6697659</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4732,9 +4722,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4749,44 +4749,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125719322</v>
+        <v>125718679</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>75011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>397309</v>
+        <v>397409</v>
       </c>
       <c r="R41" t="n">
-        <v>6697695</v>
+        <v>6697661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125718201</v>
+        <v>125719322</v>
       </c>
       <c r="B42" t="n">
         <v>78977</v>
@@ -4889,14 +4889,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
+          <t>Lövåsen, Lövåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>397560</v>
+        <v>397309</v>
       </c>
       <c r="R42" t="n">
-        <v>6697723</v>
+        <v>6697695</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125717848</v>
+        <v>125718201</v>
       </c>
       <c r="B43" t="n">
         <v>78977</v>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>397549</v>
+        <v>397560</v>
       </c>
       <c r="R43" t="n">
-        <v>6697680</v>
+        <v>6697723</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5023,19 +5023,9 @@
           <t>2025-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:55</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-06-05</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5050,39 +5040,39 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125718753</v>
+        <v>125717848</v>
       </c>
       <c r="B44" t="n">
-        <v>80115</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5093,17 +5083,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lövåsen, Lövåsen, Vrm</t>
+          <t>Lövåsmyren, Lövåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>397437</v>
+        <v>397549</v>
       </c>
       <c r="R44" t="n">
-        <v>6697664</v>
+        <v>6697680</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,9 +5120,19 @@
           <t>2025-06-05</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5147,12 +5147,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
